--- a/results/Int Task Remove ACC -0.4/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_8_permute.xlsx
@@ -440,67 +440,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6906521399467912</v>
+        <v>0.6946263930932681</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7067567654338075</v>
+        <v>0.6946263930932681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6965915811898431</v>
+        <v>0.6710086419761894</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6945894722422978</v>
+        <v>0.65709072969157</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6954316957122585</v>
+        <v>0.6583244568710952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6951878754065752</v>
+        <v>0.657969874012501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6789132713158164</v>
+        <v>0.6679650796527228</v>
       </c>
     </row>
     <row r="9">
@@ -510,327 +510,327 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6772880404267265</v>
+        <v>0.6643969558669194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6820529705410849</v>
+        <v>0.6582798664713726</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6830059565639566</v>
+        <v>0.7113510034980277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7047915773372325</v>
+        <v>0.7113510034980277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7044739153296087</v>
+        <v>0.7113510034980277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6977807179696458</v>
+        <v>0.7116686655056516</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7296946021359159</v>
+        <v>0.7052046628002628</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7354717343239774</v>
+        <v>0.7062314905250751</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7551277176065014</v>
+        <v>0.7055961665098274</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7540416738308575</v>
+        <v>0.7183841580654758</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7433226768223382</v>
+        <v>0.7527201927446783</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7416751507333872</v>
+        <v>0.7508511415499053</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7102858280294539</v>
+        <v>0.7508511415499053</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7072499352547397</v>
+        <v>0.7288885860705299</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6964717221953887</v>
+        <v>0.7312229826768081</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6776558220436386</v>
+        <v>0.7312229826768081</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6718487251069634</v>
+        <v>0.723953677352429</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6718487251069634</v>
+        <v>0.7159975015107227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.704066359076144</v>
+        <v>0.6964062634885959</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7251936471879153</v>
+        <v>0.685502662225225</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.718545040227675</v>
+        <v>0.685502662225225</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7182642990710215</v>
+        <v>0.6405207587930485</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7185819610786454</v>
+        <v>0.6430397596541783</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7263235679168863</v>
+        <v>0.6545201823283608</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7127226041934953</v>
+        <v>0.6628163153775523</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7175223148196372</v>
+        <v>0.6548378443359848</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7142495578415964</v>
+        <v>0.6601273359126799</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7153871481193197</v>
+        <v>0.6547500904293306</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7055619210828403</v>
+        <v>0.6553561631423603</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6716173901132025</v>
+        <v>0.6666735633151571</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6701892487908867</v>
+        <v>0.6895375583153247</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6570466743766441</v>
+        <v>0.69942128795624</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6570466743766441</v>
+        <v>0.6920704713811681</v>
       </c>
     </row>
     <row r="42">
@@ -840,487 +840,487 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6603187179082892</v>
+        <v>0.6811738262201539</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6599801875935953</v>
+        <v>0.6300232868903511</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.657867316093139</v>
+        <v>0.6174582473333158</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7089691627064446</v>
+        <v>0.6358457229245309</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7061032485354729</v>
+        <v>0.6479084962190909</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7084467415832945</v>
+        <v>0.6272611791699336</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6859965454925527</v>
+        <v>0.6276380572283892</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6822737822005113</v>
+        <v>0.6283918133453003</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6833152355764325</v>
+        <v>0.6242475815950806</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6889446843606128</v>
+        <v>0.6158260603418693</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6805572301727896</v>
+        <v>0.6154345566323047</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6705167206864495</v>
+        <v>0.621985599797952</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6925977082674881</v>
+        <v>0.6369686875511452</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6925977082674881</v>
+        <v>0.6457455051093464</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6909132613275668</v>
+        <v>0.6589437283424429</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6914809862968351</v>
+        <v>0.6741615399597759</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6856007611046149</v>
+        <v>0.6683251917208827</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6824464362282372</v>
+        <v>0.6606267483895731</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6824464362282372</v>
+        <v>0.6609604629410972</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7099068096318117</v>
+        <v>0.6530565470478659</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7048019223099682</v>
+        <v>0.713131587339751</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6794355140773676</v>
+        <v>0.706542909876738</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6796793343830507</v>
+        <v>0.7110040901881858</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6790461507069897</v>
+        <v>0.7010088845479638</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6748343199107907</v>
+        <v>0.6936957022702577</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6510981366920487</v>
+        <v>0.6729493945337164</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6401137376243805</v>
+        <v>0.6688483262904283</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.676175242411249</v>
+        <v>0.6507715566044803</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6765228691674865</v>
+        <v>0.6598082470122648</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6765228691674865</v>
+        <v>0.6601822712851382</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6793811137897059</v>
+        <v>0.6402273539628738</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6793811137897059</v>
+        <v>0.6256134747193837</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6888078810142639</v>
+        <v>0.5928218731249737</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6061146280054821</v>
+        <v>0.5928218731249737</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5597393637627734</v>
+        <v>0.5781931898687758</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5612461625501999</v>
+        <v>0.5414731740588037</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.53532183923627</v>
+        <v>0.5349784931584058</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5375677684894985</v>
+        <v>0.5357615005775349</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5308299807298129</v>
+        <v>0.5354807594208814</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5285840514765844</v>
+        <v>0.5363160267884852</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5281333317161881</v>
+        <v>0.5069851752973467</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5282071734181288</v>
+        <v>0.5045915626402369</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5072623492220224</v>
+        <v>0.511025600597012</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5069816080653688</v>
+        <v>0.5139946077721423</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5047356788121403</v>
+        <v>0.5154352344063805</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5030881527231892</v>
+        <v>0.5154352344063805</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5005245614623368</v>
+        <v>0.4994720496672843</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4996084962904355</v>
+        <v>0.4949439837562525</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4999261582980593</v>
+        <v>0.5030547991041967</v>
       </c>
     </row>
   </sheetData>
